--- a/docs/downloads/08082026Tduh Developer Project Sales Status 13.xlsx
+++ b/docs/downloads/08082026Tduh Developer Project Sales Status 13.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08082026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="08082026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/downloads/08082026Tduh Developer Project Sales Status 13.xlsx
+++ b/docs/downloads/08082026Tduh Developer Project Sales Status 13.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AZ16"/>
+  <dimension ref="A2:AW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -537,9 +537,6 @@
     <col width="9" customWidth="1" min="47" max="47"/>
     <col width="9" customWidth="1" min="48" max="48"/>
     <col width="9" customWidth="1" min="49" max="49"/>
-    <col width="9" customWidth="1" min="50" max="50"/>
-    <col width="9" customWidth="1" min="51" max="51"/>
-    <col width="9" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -597,11 +594,8 @@
       <c r="AR3" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="AU3" s="3" t="n">
+      <c r="AU3" s="4" t="n">
         <v>46241</v>
-      </c>
-      <c r="AX3" s="4" t="n">
-        <v>46242</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -837,32 +831,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="AU4" s="5" t="inlineStr">
+      <c r="AU4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="AV4" s="5" t="inlineStr">
+      <c r="AV4" s="6" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AW4" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="AX4" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NEW SALES </t>
-        </is>
-      </c>
-      <c r="AY4" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL SOLD</t>
-        </is>
-      </c>
-      <c r="AZ4" s="6" t="inlineStr">
+      <c r="AW4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1040,26 +1019,15 @@
         <f>AS5/$E$5</f>
         <v/>
       </c>
-      <c r="AU5" s="9">
+      <c r="AU5" s="11">
         <f>AV5-AS5</f>
         <v/>
       </c>
-      <c r="AV5" s="9" t="n">
+      <c r="AV5" s="11" t="n">
         <v>319</v>
       </c>
-      <c r="AW5" s="10">
+      <c r="AW5" s="12">
         <f>AV5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AX5" s="11">
-        <f>AY5-AV5</f>
-        <v/>
-      </c>
-      <c r="AY5" s="11" t="n">
-        <v>321</v>
-      </c>
-      <c r="AZ5" s="12">
-        <f>AY5/$E$5</f>
         <v/>
       </c>
     </row>
@@ -1236,26 +1204,15 @@
         <f>AS6/$E$6</f>
         <v/>
       </c>
-      <c r="AU6" s="9">
+      <c r="AU6" s="11">
         <f>AV6-AS6</f>
         <v/>
       </c>
-      <c r="AV6" s="9" t="n">
+      <c r="AV6" s="11" t="n">
         <v>112</v>
       </c>
-      <c r="AW6" s="10">
+      <c r="AW6" s="12">
         <f>AV6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AX6" s="11">
-        <f>AY6-AV6</f>
-        <v/>
-      </c>
-      <c r="AY6" s="11" t="n">
-        <v>113</v>
-      </c>
-      <c r="AZ6" s="12">
-        <f>AY6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -1431,26 +1388,15 @@
         <f>AS7/$E$7</f>
         <v/>
       </c>
-      <c r="AU7" s="9">
+      <c r="AU7" s="11">
         <f>AV7-AS7</f>
         <v/>
       </c>
-      <c r="AV7" s="9" t="n">
+      <c r="AV7" s="11" t="n">
         <v>985</v>
       </c>
-      <c r="AW7" s="10">
+      <c r="AW7" s="12">
         <f>AV7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AX7" s="11">
-        <f>AY7-AV7</f>
-        <v/>
-      </c>
-      <c r="AY7" s="11" t="n">
-        <v>986</v>
-      </c>
-      <c r="AZ7" s="12">
-        <f>AY7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -1627,26 +1573,15 @@
         <f>AS8/$E$8</f>
         <v/>
       </c>
-      <c r="AU8" s="9">
+      <c r="AU8" s="11">
         <f>AV8-AS8</f>
         <v/>
       </c>
-      <c r="AV8" s="9" t="n">
+      <c r="AV8" s="11" t="n">
         <v>1119</v>
       </c>
-      <c r="AW8" s="10">
+      <c r="AW8" s="12">
         <f>AV8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AX8" s="11">
-        <f>AY8-AV8</f>
-        <v/>
-      </c>
-      <c r="AY8" s="11" t="n">
-        <v>1119</v>
-      </c>
-      <c r="AZ8" s="12">
-        <f>AY8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -1823,26 +1758,15 @@
         <f>AS9/$E$9</f>
         <v/>
       </c>
-      <c r="AU9" s="9">
+      <c r="AU9" s="11">
         <f>AV9-AS9</f>
         <v/>
       </c>
-      <c r="AV9" s="9" t="n">
+      <c r="AV9" s="11" t="n">
         <v>491</v>
       </c>
-      <c r="AW9" s="10">
+      <c r="AW9" s="12">
         <f>AV9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AX9" s="11">
-        <f>AY9-AV9</f>
-        <v/>
-      </c>
-      <c r="AY9" s="11" t="n">
-        <v>491</v>
-      </c>
-      <c r="AZ9" s="12">
-        <f>AY9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -2018,26 +1942,15 @@
         <f>AS10/$E$10</f>
         <v/>
       </c>
-      <c r="AU10" s="9">
+      <c r="AU10" s="11">
         <f>AV10-AS10</f>
         <v/>
       </c>
-      <c r="AV10" s="9" t="n">
+      <c r="AV10" s="11" t="n">
         <v>465</v>
       </c>
-      <c r="AW10" s="10">
+      <c r="AW10" s="12">
         <f>AV10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AX10" s="11">
-        <f>AY10-AV10</f>
-        <v/>
-      </c>
-      <c r="AY10" s="11" t="n">
-        <v>466</v>
-      </c>
-      <c r="AZ10" s="12">
-        <f>AY10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -2213,26 +2126,15 @@
         <f>AS11/$E$11</f>
         <v/>
       </c>
-      <c r="AU11" s="9">
+      <c r="AU11" s="11">
         <f>AV11-AS11</f>
         <v/>
       </c>
-      <c r="AV11" s="9" t="n">
+      <c r="AV11" s="11" t="n">
         <v>235</v>
       </c>
-      <c r="AW11" s="10">
+      <c r="AW11" s="12">
         <f>AV11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AX11" s="11">
-        <f>AY11-AV11</f>
-        <v/>
-      </c>
-      <c r="AY11" s="11" t="n">
-        <v>235</v>
-      </c>
-      <c r="AZ11" s="12">
-        <f>AY11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -2409,26 +2311,15 @@
         <f>AS12/$E$12</f>
         <v/>
       </c>
-      <c r="AU12" s="9">
+      <c r="AU12" s="11">
         <f>AV12-AS12</f>
         <v/>
       </c>
-      <c r="AV12" s="9" t="n">
+      <c r="AV12" s="11" t="n">
         <v>608</v>
       </c>
-      <c r="AW12" s="10">
+      <c r="AW12" s="12">
         <f>AV12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AX12" s="11">
-        <f>AY12-AV12</f>
-        <v/>
-      </c>
-      <c r="AY12" s="11" t="n">
-        <v>609</v>
-      </c>
-      <c r="AZ12" s="12">
-        <f>AY12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -2604,26 +2495,15 @@
         <f>AS13/$E$13</f>
         <v/>
       </c>
-      <c r="AU13" s="9">
+      <c r="AU13" s="11">
         <f>AV13-AS13</f>
         <v/>
       </c>
-      <c r="AV13" s="9" t="n">
+      <c r="AV13" s="11" t="n">
         <v>1139</v>
       </c>
-      <c r="AW13" s="10">
+      <c r="AW13" s="12">
         <f>AV13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AX13" s="11">
-        <f>AY13-AV13</f>
-        <v/>
-      </c>
-      <c r="AY13" s="11" t="n">
-        <v>1140</v>
-      </c>
-      <c r="AZ13" s="12">
-        <f>AY13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -2799,26 +2679,15 @@
         <f>AS14/$E$14</f>
         <v/>
       </c>
-      <c r="AU14" s="9">
+      <c r="AU14" s="11">
         <f>AV14-AS14</f>
         <v/>
       </c>
-      <c r="AV14" s="9" t="n">
+      <c r="AV14" s="11" t="n">
         <v>124</v>
       </c>
-      <c r="AW14" s="10">
+      <c r="AW14" s="12">
         <f>AV14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AX14" s="11">
-        <f>AY14-AV14</f>
-        <v/>
-      </c>
-      <c r="AY14" s="11" t="n">
-        <v>124</v>
-      </c>
-      <c r="AZ14" s="12">
-        <f>AY14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -2930,26 +2799,15 @@
         <f>AS15/$E$15</f>
         <v/>
       </c>
-      <c r="AU15" s="9">
+      <c r="AU15" s="11">
         <f>AV15-AS15</f>
         <v/>
       </c>
-      <c r="AV15" s="9" t="n">
+      <c r="AV15" s="11" t="n">
         <v>659</v>
       </c>
-      <c r="AW15" s="10">
+      <c r="AW15" s="12">
         <f>AV15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AX15" s="11">
-        <f>AY15-AV15</f>
-        <v/>
-      </c>
-      <c r="AY15" s="11" t="n">
-        <v>659</v>
-      </c>
-      <c r="AZ15" s="12">
-        <f>AY15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -3121,31 +2979,20 @@
         <f>AS16/$E$16</f>
         <v/>
       </c>
-      <c r="AU16" s="9">
+      <c r="AU16" s="11">
         <f>AV16-AS16</f>
         <v/>
       </c>
-      <c r="AV16" s="9" t="n">
+      <c r="AV16" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="AW16" s="10">
+      <c r="AW16" s="12">
         <f>AV16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AX16" s="11">
-        <f>AY16-AV16</f>
-        <v/>
-      </c>
-      <c r="AY16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" s="12">
-        <f>AY16/$E$16</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="15">
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="AU3:AW3"/>
     <mergeCell ref="W3:Y3"/>
@@ -3154,7 +3001,6 @@
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="AC3:AE3"/>
     <mergeCell ref="AF3:AH3"/>
-    <mergeCell ref="AX3:AZ3"/>
     <mergeCell ref="K3:M3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="Z3:AB3"/>
